--- a/human_resources_forms/026_landscaping_job_application_form--human_resources_forms.xlsx
+++ b/human_resources_forms/026_landscaping_job_application_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Job Questions</t>
+          <t>Job Questions Parent</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Available Start Date</t>
+          <t>Available Start Date Parent</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Resume Parent</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Consent</t>
+          <t>Consent Parent</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
